--- a/data/Q&A.xlsx
+++ b/data/Q&A.xlsx
@@ -1,353 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17940"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17940" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>问题</t>
-  </si>
-  <si>
-    <t>SQL</t>
-  </si>
-  <si>
-    <t>学历本科及以上的男性客户，年龄大于50岁的有多少个</t>
-  </si>
-  <si>
-    <t xml:space="preserve">select count(*)
-from ads_cust_info_d a
-left join dim_public b on a.edu_cd = b.code and b.code_type_id='600' 
-left join dim_public c on a.gender_cd = c.code and c.code_type_id='500'
-where b.describe  in ('博士','硕士','学士') and c.describe in ('男')
-and a.cust_age&gt;50 </t>
-  </si>
-  <si>
-    <t>不同客户年龄段资产分布情况，如下规则：
-1、小于30
-2、大于等于30，小于50
-3、大于等于50，小于60
-4、大于60</t>
-  </si>
-  <si>
-    <t>select case when cust_age&lt;30 then '&lt;30'
-     when cust_age&gt;=30 and cust_age&lt;50 then '[30,50)'
-     when cust_age&gt;=50 and cust_age&lt;60 then '[50,60)'
-     when cust_age&gt;=60 then '[60,)'
-    end as cust_age_type
-  ,sum(coalesce(b.nm_tot_aset,0)+coalesce(b.fc_pur_aset,0)) as aset 
-from ads_cust_info_d a
-left join dws_cust_aset_d b on a.pty_id=b.pty_id and b.data_dt='20260331'
-where a.data_dt='20260531'
-group by case when cust_age&lt;30 then '&lt;30'
-     when cust_age&gt;=30 and cust_age&lt;50 then '[30,50)'
-     when cust_age&gt;=50 and cust_age&lt;60 then '[50,60)'
-     when cust_age&gt;=60 then '[60,)'
-    end;</t>
-  </si>
-  <si>
-    <t>钻石卡男性客户，年龄大于40岁，持有比亚迪市值超过1000元，他在26年Q1的盈亏情况</t>
-  </si>
-  <si>
-    <t>with custinfo as
-(select pty_id
-from ads_cust_info_d a 
-left join dim_public b on a.cust_lvl_cd=b.code and b.code_type_id='100'
-left join dim_public c on a.gender_cd=c.code and c.code_type_id='500'
-where b.describe='紫金理财钻石卡客户' and c.describe in ('男')
-and a.cust_age&gt;40
-),
-prdtinfo as
-(select a.pty_id,sum(a.mkt_val) as mkt_val
-from dwd_cust_hold_d a
-inner join dim_product b on a.prdt_id=b.prdt_id
-where b.prdt_name='比亚迪' and a.data_dt='20260331'
-and exists(select 1 from custinfo z where a.pty_id=z.pty_id)
-group by a.pty_id
-having sum(a.mkt_val)&gt;1000
-)
-select a.pty_id
-     ,coalesce(c.nm_tot_aset,0)+coalesce(c.fc_pur_aset,0) as bgn_aset
-     ,coalesce(b.nm_tot_aset,0)+coalesce(b.fc_pur_aset,0) as end_aset
-     ,coalesce(d.aset_in,0) as aset_in
-     ,coalesce(d.aset_out,0) as aset_out
-     ,coalesce(b.nm_tot_aset,0)+coalesce(b.fc_pur_aset,0)-coalesce(c.nm_tot_aset,0)+coalesce(c.fc_pur_aset,0)+coalesce(d.aset_out,0)-coalesce(d.aset_in,0) as aset_pft
-from prdtinfo a
-left join dws_cust_aset_d b on a.pty_id=b.pty_id and b.data_dt='20260331'
-left join dws_cust_aset_d c on a.pty_id=c.pty_id and c.data_dt='20260101'  --准确的话应该是20251231，暂时以20260101代替
-left join 
-(
-select pty_id
-      ,sum(cash_in)+sum(tran_in)+sum(assign_in) as aset_in
-      ,sum(cash_out)+sum(tran_out)+sum(assign_out) as aset_out
-from dws_cust_fin_d
-where data_dt between '20260101' and '20260331'
-group by pty_id
-) d on a.pty_id=d.pty_id;</t>
-  </si>
-  <si>
-    <t>分公司各营业部的客户省份分析统计</t>
-  </si>
-  <si>
-    <t>select b.up_org_name,b.org_name,a.prov_name,a.city_name,count(*) as cnt
-from ads_cust_info_d a
-inner join dim_branch b on a.org_id=b.org_id
-group by b.up_org_name,b.org_name,a.prov_name,a.city_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26年Q1交易过招商银行，且26年Q1末普通账户持有中国平安的客户
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-with cust_tran as
-(
-select pty_id,prdt_id,sum(buy_amt) as buy_tot,sum(sell_amt) as sell_tot 
-from dwd_cust_tran_d
-where data_dt between '20260101' and '20260331' 
-and prdt_id in (
-select prdt_id from dim_product
-where prdt_name='招商银行' and prdt_type_name='A股'
-)
-group by pty_id,prdt_id
-)
-select a.pty_id
-from cust_tran a
-inner join 
-(
-select a.*
-from dwd_cust_hold_d a
-where prdt_id in (select prdt_id from dim_product where prdt_name='中国平安' and prdt_type_name='A股')
-and a.data_dt='20260331' and a.sys_source='nm'
-) b on a.pty_id=b.pty_id
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26年Q1日均资产大于30万的客户，股票交易量大于10万的，其持有的产品属于哪些产品大类
-</t>
-  </si>
-  <si>
-    <t>with cust_avg_30 as 
-(
-select pty_id,round(sum(coalesce(nm_tot_aset,0)+coalesce(fc_pur_aset,0))/((to_date('20260331','yyyymmdd')-to_date('20260101','yyyymmdd'))::integer+1),2) as avg_aset
-from dws_cust_aset_d
-group by pty_id
-having sum(coalesce(nm_tot_aset,0)+coalesce(fc_pur_aset,0))/((to_date('20260331','yyyymmdd')-to_date('20260101','yyyymmdd'))::integer+1)&gt;300000
-), cust_tran as
-(
-select a.pty_id,sum(b.buy_amt)+sum(b.sell_amt) as tran_amt
-from dws_cust_aset_d a
-left join dwd_cust_tran_d b on a.pty_id=b.pty_id and b.data_dt between '20260101' and '20260331'
-inner join dim_product c on b.prdt_id=c.prdt_id and c.up_prdt_type_id='PT040000'
-group by a.pty_id
-having sum(b.buy_amt)+sum(b.sell_amt)&gt;100000
-)
-select c.up_prdt_type_name,c.prdt_type_name,sum(mkt_val) as mkt_val
-from cust_tran a
-inner join dwd_cust_hold_d b on a.pty_id=b.pty_id and b.data_dt='20260331'
-inner join dim_product c on b.prdt_id=c.prdt_id
-group by c.prdt_type_name,c.up_prdt_type_name
-;</t>
-  </si>
-  <si>
-    <t>查询26年1月10日到26年2月15日期间，科创板交易量大于25万的客户营业部分布情况</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-select c.up_org_name,c.org_name,sum(b.tran_amt) as tran_amt
-from ads_cust_info_d a
-inner join 
-(
-select a.pty_id,sum(buy_amt)+sum(sell_amt) as tran_amt
-from dwd_cust_tran_d a
-inner join dim_product b on a.prdt_id=b.prdt_id and b.prdt_type_name='科创板'
-where a.data_dt between '20260110' and '20260215'
-group by a.pty_id
-having sum(buy_amt)+sum(sell_amt)&gt;250000
-) b on a.pty_id=b.pty_id
-left join dim_branch c on a.org_id=c.org_id
-group by c.up_org_name,c.org_name;</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -663,161 +487,161 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -873,11 +697,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1137,105 +1024,256 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
-    <col min="2" max="2" width="50.625" customWidth="1"/>
-    <col min="3" max="3" width="104.5" customWidth="1"/>
+    <col width="50.625" customWidth="1" min="2" max="2"/>
+    <col width="104.5" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="85.5" customHeight="1">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>学历本科及以上的男性客户，年龄大于50岁的有多少个</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">select count(*)
+from ads_cust_info_d a
+left join dim_public b on a.edu_cd = b.code and b.code_type_id='600' 
+left join dim_public c on a.gender_cd = c.code and c.code_type_id='500'
+where b.describe  in ('博士','硕士','学士') and c.describe in ('男')
+and a.cust_age&gt;50 </t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="199.5" customHeight="1">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>不同客户年龄段资产分布情况，如下规则：
+1、小于30
+2、大于等于30，小于50
+3、大于等于50，小于60
+4、大于60</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>select case when cust_age&lt;30 then '&lt;30'
+     when cust_age&gt;=30 and cust_age&lt;50 then '[30,50)'
+     when cust_age&gt;=50 and cust_age&lt;60 then '[50,60)'
+     when cust_age&gt;=60 then '[60,)'
+    end as cust_age_type
+  ,sum(coalesce(b.nm_tot_aset,0)+coalesce(b.fc_pur_aset,0)) as aset 
+from ads_cust_info_d a
+left join dws_cust_aset_d b on a.pty_id=b.pty_id and b.data_dt='20260331'
+where a.data_dt='20260531'
+group by case when cust_age&lt;30 then '&lt;30'
+     when cust_age&gt;=30 and cust_age&lt;50 then '[30,50)'
+     when cust_age&gt;=50 and cust_age&lt;60 then '[50,60)'
+     when cust_age&gt;=60 then '[60,)'
+    end;</t>
+        </is>
+      </c>
     </row>
-    <row r="2" ht="85.5" spans="1:3">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="4" ht="409.5" customHeight="1">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>钻石卡男性客户，年龄大于40岁，持有比亚迪市值超过1000元，他在26年Q1的盈亏情况</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>with custinfo as
+(select pty_id
+from ads_cust_info_d a 
+left join dim_public b on a.cust_lvl_cd=b.code and b.code_type_id='100'
+left join dim_public c on a.gender_cd=c.code and c.code_type_id='500'
+where b.describe='紫金理财钻石卡客户' and c.describe in ('男')
+and a.cust_age&gt;40
+),
+prdtinfo as
+(select a.pty_id,sum(a.mkt_val) as mkt_val
+from dwd_cust_hold_d a
+inner join dim_product b on a.prdt_id=b.prdt_id
+where b.prdt_name='比亚迪' and a.data_dt='20260331'
+and exists(select 1 from custinfo z where a.pty_id=z.pty_id)
+group by a.pty_id
+having sum(a.mkt_val)&gt;1000
+)
+select a.pty_id
+     ,coalesce(c.nm_tot_aset,0)+coalesce(c.fc_pur_aset,0) as bgn_aset
+     ,coalesce(b.nm_tot_aset,0)+coalesce(b.fc_pur_aset,0) as end_aset
+     ,coalesce(d.aset_in,0) as aset_in
+     ,coalesce(d.aset_out,0) as aset_out
+     ,coalesce(b.nm_tot_aset,0)+coalesce(b.fc_pur_aset,0)-(coalesce(c.nm_tot_aset,0)+coalesce(c.fc_pur_aset,0))+coalesce(d.aset_out,0)-coalesce(d.aset_in,0) as aset_pft
+from prdtinfo a
+left join dws_cust_aset_d b on a.pty_id=b.pty_id and b.data_dt='20260331'
+left join dws_cust_aset_d c on a.pty_id=c.pty_id and c.data_dt='20260101'  --准确的话应该是20251231，暂时以20260101代替
+left join 
+(
+select pty_id
+      ,sum(cash_in)+sum(tran_in)+sum(assign_in) as aset_in
+      ,sum(cash_out)+sum(tran_out)+sum(assign_out) as aset_out
+from dws_cust_fin_d
+where data_dt between '20260101' and '20260331'
+group by pty_id
+) d on a.pty_id=d.pty_id;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="57" customHeight="1">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>分公司各营业部的客户省份分析统计</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>select b.up_org_name,b.org_name,a.prov_name,a.city_name,count(*) as cnt
+from ads_cust_info_d a
+inner join dim_branch b on a.org_id=b.org_id
+group by b.up_org_name,b.org_name,a.prov_name,a.city_name</t>
+        </is>
+      </c>
     </row>
-    <row r="3" ht="199.5" spans="1:3">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="6" ht="313.5" customHeight="1">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26年Q1交易过招商银行，且26年Q1末普通账户持有中国平安的客户
+</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+with cust_tran as
+(
+select pty_id,prdt_id,sum(buy_amt) as buy_tot,sum(sell_amt) as sell_tot 
+from dwd_cust_tran_d
+where data_dt between '20260101' and '20260331' 
+and prdt_id in (
+select prdt_id from dim_product
+where prdt_name='招商银行' and prdt_type_name='A股'
+)
+group by pty_id,prdt_id
+)
+select a.pty_id
+from cust_tran a
+inner join 
+(
+select a.*
+from dwd_cust_hold_d a
+where prdt_id in (select prdt_id from dim_product where prdt_name='中国平安' and prdt_type_name='A股')
+and a.data_dt='20260331' and a.sys_source='nm'
+) b on a.pty_id=b.pty_id
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="327.75" customHeight="1">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26年Q1日均资产大于30万的客户，股票交易量大于10万的，其持有的产品属于哪些产品大类
+</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>with cust_avg_30 as 
+(
+select pty_id,round(sum(coalesce(nm_tot_aset,0)+coalesce(fc_pur_aset,0))/((to_date('20260331','yyyymmdd')-to_date('20260101','yyyymmdd'))::integer+1),2) as avg_aset
+from dws_cust_aset_d
+group by pty_id
+having sum(coalesce(nm_tot_aset,0)+coalesce(fc_pur_aset,0))/((to_date('20260331','yyyymmdd')-to_date('20260101','yyyymmdd'))::integer+1)&gt;300000
+), cust_tran as
+(
+select a.pty_id,sum(b.buy_amt)+sum(b.sell_amt) as tran_amt
+from dws_cust_aset_d a
+left join dwd_cust_tran_d b on a.pty_id=b.pty_id and b.data_dt between '20260101' and '20260331'
+inner join dim_product c on b.prdt_id=c.prdt_id and c.up_prdt_type_id='PT040000'
+group by a.pty_id
+having sum(b.buy_amt)+sum(b.sell_amt)&gt;100000
+)
+select c.up_prdt_type_name,c.prdt_type_name,sum(mkt_val) as mkt_val
+from cust_tran a
+inner join dwd_cust_hold_d b on a.pty_id=b.pty_id and b.data_dt='20260331'
+inner join dim_product c on b.prdt_id=c.prdt_id
+group by c.prdt_type_name,c.up_prdt_type_name
+;</t>
+        </is>
+      </c>
     </row>
-    <row r="4" ht="409.5" spans="1:3">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="8" ht="199.5" customHeight="1">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" ht="57" spans="1:3">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" ht="313.5" spans="1:3">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" ht="327.75" spans="1:3">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" ht="199.5" spans="1:3">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>16</v>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>查询26年1月10日到26年2月15日期间，科创板交易量大于25万的客户营业部分布情况</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+select c.up_org_name,c.org_name,sum(b.tran_amt) as tran_amt
+from ads_cust_info_d a
+inner join 
+(
+select a.pty_id,sum(buy_amt)+sum(sell_amt) as tran_amt
+from dwd_cust_tran_d a
+inner join dim_product b on a.prdt_id=b.prdt_id and b.prdt_type_name='科创板'
+where a.data_dt between '20260110' and '20260215'
+group by a.pty_id
+having sum(buy_amt)+sum(sell_amt)&gt;250000
+) b on a.pty_id=b.pty_id
+left join dim_branch c on a.org_id=c.org_id
+group by c.up_org_name,c.org_name;</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>